--- a/artfynd/A 17099-2025 artfynd.xlsx
+++ b/artfynd/A 17099-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120159770</v>
+        <v>120159769</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159769</v>
+        <v>120159767</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703482</v>
+        <v>703463</v>
       </c>
       <c r="R3" t="n">
-        <v>7131546</v>
+        <v>7131557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,12 +872,7 @@
         <v>120159768</v>
       </c>
       <c r="B4" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,108 +963,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>120159767</v>
-      </c>
-      <c r="B5" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Strandåker, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>703463</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7131557</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
